--- a/evaluation_forms/012_vector_database_model_evaluation_form--evaluation_forms.xlsx
+++ b/evaluation_forms/012_vector_database_model_evaluation_form--evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'user_1'}</t>
+          <t>user_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'User 1'}</t>
+          <t>User 1</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'user_2'}</t>
+          <t>user_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'User 2'}</t>
+          <t>User 2</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'user_3'}</t>
+          <t>user_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'User 3'}</t>
+          <t>User 3</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'user_4'}</t>
+          <t>user_4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'User 4'}</t>
+          <t>User 4</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'user_5'}</t>
+          <t>user_5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'User 5'}</t>
+          <t>User 5</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'user_6'}</t>
+          <t>user_6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'User 6'}</t>
+          <t>User 6</t>
         </is>
       </c>
     </row>
@@ -1047,12 +1047,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'user_7'}</t>
+          <t>user_7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'User 7'}</t>
+          <t>User 7</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'user_8'}</t>
+          <t>user_8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'User 8'}</t>
+          <t>User 8</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'user_9'}</t>
+          <t>user_9</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'User 9'}</t>
+          <t>User 9</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1098,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'user_10'}</t>
+          <t>user_10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'User 10'}</t>
+          <t>User 10</t>
         </is>
       </c>
     </row>
@@ -1115,12 +1115,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'user_11'}</t>
+          <t>user_11</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'User 11'}</t>
+          <t>User 11</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'user_12'}</t>
+          <t>user_12</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'User 12'}</t>
+          <t>User 12</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'user_13'}</t>
+          <t>user_13</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'User 13'}</t>
+          <t>User 13</t>
         </is>
       </c>
     </row>
@@ -1166,12 +1166,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'user_14'}</t>
+          <t>user_14</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'User 14'}</t>
+          <t>User 14</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'user_15'}</t>
+          <t>user_15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'User 15'}</t>
+          <t>User 15</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'user_16'}</t>
+          <t>user_16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'User 16'}</t>
+          <t>User 16</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1217,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'user_17'}</t>
+          <t>user_17</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'User 17'}</t>
+          <t>User 17</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'user_18'}</t>
+          <t>user_18</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'User 18'}</t>
+          <t>User 18</t>
         </is>
       </c>
     </row>
@@ -1251,12 +1251,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'user_19'}</t>
+          <t>user_19</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'User 19'}</t>
+          <t>User 19</t>
         </is>
       </c>
     </row>
@@ -1268,12 +1268,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'user_20'}</t>
+          <t>user_20</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'User 20'}</t>
+          <t>User 20</t>
         </is>
       </c>
     </row>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'user_21'}</t>
+          <t>user_21</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'User 21'}</t>
+          <t>User 21</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'user_22'}</t>
+          <t>user_22</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'User 22'}</t>
+          <t>User 22</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'user_23'}</t>
+          <t>user_23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'User 23'}</t>
+          <t>User 23</t>
         </is>
       </c>
     </row>
@@ -1336,12 +1336,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'user_24'}</t>
+          <t>user_24</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'User 24'}</t>
+          <t>User 24</t>
         </is>
       </c>
     </row>
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'user_25'}</t>
+          <t>user_25</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 'User 25'}</t>
+          <t>User 25</t>
         </is>
       </c>
     </row>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_'user_26'}</t>
+          <t>user_26</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 'User 26'}</t>
+          <t>User 26</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_'user_27'}</t>
+          <t>user_27</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': 'User 27'}</t>
+          <t>User 27</t>
         </is>
       </c>
     </row>
@@ -1404,12 +1404,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_'user_28'}</t>
+          <t>user_28</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': 'User 28'}</t>
+          <t>User 28</t>
         </is>
       </c>
     </row>
@@ -1421,12 +1421,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'value':_'user_29'}</t>
+          <t>user_29</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'value': 'User 29'}</t>
+          <t>User 29</t>
         </is>
       </c>
     </row>
@@ -1438,12 +1438,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'value':_'user_30'}</t>
+          <t>user_30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'value': 'User 30'}</t>
+          <t>User 30</t>
         </is>
       </c>
     </row>
@@ -1455,12 +1455,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'value':_'user_31'}</t>
+          <t>user_31</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'value': 'User 31'}</t>
+          <t>User 31</t>
         </is>
       </c>
     </row>
@@ -1472,12 +1472,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'value':_'user_32'}</t>
+          <t>user_32</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'value': 'User 32'}</t>
+          <t>User 32</t>
         </is>
       </c>
     </row>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'value':_'user_33'}</t>
+          <t>user_33</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'value': 'User 33'}</t>
+          <t>User 33</t>
         </is>
       </c>
     </row>
@@ -1506,12 +1506,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'value':_'user_34'}</t>
+          <t>user_34</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'value': 'User 34'}</t>
+          <t>User 34</t>
         </is>
       </c>
     </row>
@@ -1523,12 +1523,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'value':_'user_35'}</t>
+          <t>user_35</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'value': 'User 35'}</t>
+          <t>User 35</t>
         </is>
       </c>
     </row>
@@ -1540,12 +1540,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'value':_'user_36'}</t>
+          <t>user_36</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'value': 'User 36'}</t>
+          <t>User 36</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'value':_'user_37'}</t>
+          <t>user_37</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'value': 'User 37'}</t>
+          <t>User 37</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'value':_'user_38'}</t>
+          <t>user_38</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'value': 'User 38'}</t>
+          <t>User 38</t>
         </is>
       </c>
     </row>
@@ -1591,12 +1591,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'value':_'user_39'}</t>
+          <t>user_39</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'value': 'User 39'}</t>
+          <t>User 39</t>
         </is>
       </c>
     </row>
@@ -1608,12 +1608,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'value':_'user_40'}</t>
+          <t>user_40</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'value': 'User 40'}</t>
+          <t>User 40</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'value':_'user_41'}</t>
+          <t>user_41</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'value': 'User 41'}</t>
+          <t>User 41</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'value':_'user_42'}</t>
+          <t>user_42</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'value': 'User 42'}</t>
+          <t>User 42</t>
         </is>
       </c>
     </row>
@@ -1659,12 +1659,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'value':_'user_43'}</t>
+          <t>user_43</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'value': 'User 43'}</t>
+          <t>User 43</t>
         </is>
       </c>
     </row>
@@ -1676,12 +1676,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'value':_'user_44'}</t>
+          <t>user_44</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'value': 'User 44'}</t>
+          <t>User 44</t>
         </is>
       </c>
     </row>
@@ -1693,12 +1693,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'value':_'user_45'}</t>
+          <t>user_45</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'value': 'User 45'}</t>
+          <t>User 45</t>
         </is>
       </c>
     </row>
@@ -1710,12 +1710,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'value':_'user_46'}</t>
+          <t>user_46</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'value': 'User 46'}</t>
+          <t>User 46</t>
         </is>
       </c>
     </row>
@@ -1727,12 +1727,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'value':_'user_47'}</t>
+          <t>user_47</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'value': 'User 47'}</t>
+          <t>User 47</t>
         </is>
       </c>
     </row>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'value':_'user_48'}</t>
+          <t>user_48</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'value': 'User 48'}</t>
+          <t>User 48</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'value':_'user_49'}</t>
+          <t>user_49</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'value': 'User 49'}</t>
+          <t>User 49</t>
         </is>
       </c>
     </row>
@@ -1778,12 +1778,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'value':_'user_50'}</t>
+          <t>user_50</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'value': 'User 50'}</t>
+          <t>User 50</t>
         </is>
       </c>
     </row>
